--- a/output/yearly_total_coral_cover_iteration_60_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_60_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.260972886569769</v>
+        <v>1.26157175266936</v>
       </c>
       <c r="C3" t="n">
-        <v>4.6156543249023</v>
+        <v>4.670759823541673</v>
       </c>
       <c r="D3" t="n">
-        <v>6.18622308910429</v>
+        <v>6.082089110114832</v>
       </c>
       <c r="E3" t="n">
-        <v>12.06285030057636</v>
+        <v>12.01442068632586</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.398515970670191</v>
+        <v>1.391877831645445</v>
       </c>
       <c r="C4" t="n">
-        <v>5.075862221296164</v>
+        <v>5.231826807628022</v>
       </c>
       <c r="D4" t="n">
-        <v>6.496954710206543</v>
+        <v>6.40837259049153</v>
       </c>
       <c r="E4" t="n">
-        <v>12.9713329021729</v>
+        <v>13.032077229765</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.577720835861616</v>
+        <v>1.570846606901767</v>
       </c>
       <c r="C5" t="n">
-        <v>5.690456897051117</v>
+        <v>5.964971877421607</v>
       </c>
       <c r="D5" t="n">
-        <v>6.928256225093541</v>
+        <v>6.768378191450608</v>
       </c>
       <c r="E5" t="n">
-        <v>14.19643395800627</v>
+        <v>14.30419667577398</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.777645814969693</v>
+        <v>1.771152915485142</v>
       </c>
       <c r="C6" t="n">
-        <v>6.456805883640309</v>
+        <v>6.861645218226421</v>
       </c>
       <c r="D6" t="n">
-        <v>7.282264578867372</v>
+        <v>7.216835116327973</v>
       </c>
       <c r="E6" t="n">
-        <v>15.51671627747738</v>
+        <v>15.84963325003953</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>2.001294841758198</v>
+        <v>2.002312797362219</v>
       </c>
       <c r="C7" t="n">
-        <v>7.415588253504387</v>
+        <v>7.880251905912391</v>
       </c>
       <c r="D7" t="n">
-        <v>7.656618336047758</v>
+        <v>7.677675803634386</v>
       </c>
       <c r="E7" t="n">
-        <v>17.07350143131034</v>
+        <v>17.560240506909</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.222227295730459</v>
+        <v>1.223186607476612</v>
       </c>
       <c r="C8" t="n">
-        <v>5.198029876125665</v>
+        <v>5.465112561929987</v>
       </c>
       <c r="D8" t="n">
-        <v>5.91941250148211</v>
+        <v>5.87102654243543</v>
       </c>
       <c r="E8" t="n">
-        <v>12.33966967333823</v>
+        <v>12.55932571184203</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.536652599092213</v>
+        <v>1.527262609843897</v>
       </c>
       <c r="C9" t="n">
-        <v>6.509434551381932</v>
+        <v>6.667114235774661</v>
       </c>
       <c r="D9" t="n">
-        <v>6.447859851439691</v>
+        <v>6.498929460487083</v>
       </c>
       <c r="E9" t="n">
-        <v>14.49394700191383</v>
+        <v>14.69330630610564</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.863297350223762</v>
+        <v>1.843953332620659</v>
       </c>
       <c r="C10" t="n">
-        <v>8.029857774954314</v>
+        <v>7.970523643037298</v>
       </c>
       <c r="D10" t="n">
-        <v>6.973511473454778</v>
+        <v>7.110485455354424</v>
       </c>
       <c r="E10" t="n">
-        <v>16.86666659863285</v>
+        <v>16.92496243101238</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.19944547674066</v>
+        <v>2.16548641037249</v>
       </c>
       <c r="C11" t="n">
-        <v>9.711605746302716</v>
+        <v>9.32984362864272</v>
       </c>
       <c r="D11" t="n">
-        <v>7.451432447810525</v>
+        <v>7.731927171112607</v>
       </c>
       <c r="E11" t="n">
-        <v>19.3624836708539</v>
+        <v>19.22725721012782</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.536617277288067</v>
+        <v>2.477023487420702</v>
       </c>
       <c r="C12" t="n">
-        <v>11.49695563215145</v>
+        <v>10.78196032205523</v>
       </c>
       <c r="D12" t="n">
-        <v>8.042081337368572</v>
+        <v>8.339132958918649</v>
       </c>
       <c r="E12" t="n">
-        <v>22.07565424680809</v>
+        <v>21.59811676839458</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.86077025441881</v>
+        <v>2.778315504960552</v>
       </c>
       <c r="C13" t="n">
-        <v>13.34594887720433</v>
+        <v>12.29476581349462</v>
       </c>
       <c r="D13" t="n">
-        <v>8.584854331306303</v>
+        <v>8.863241510599318</v>
       </c>
       <c r="E13" t="n">
-        <v>24.79157346292944</v>
+        <v>23.93632282905449</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.64360273654184</v>
+        <v>1.599679344253838</v>
       </c>
       <c r="C14" t="n">
-        <v>9.290357065103908</v>
+        <v>8.715936483349099</v>
       </c>
       <c r="D14" t="n">
-        <v>6.485896573152467</v>
+        <v>6.734612536546355</v>
       </c>
       <c r="E14" t="n">
-        <v>17.41985637479821</v>
+        <v>17.05022836414929</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.69300428101954</v>
+        <v>1.624861172867768</v>
       </c>
       <c r="C15" t="n">
-        <v>10.27774981865014</v>
+        <v>9.342340606043775</v>
       </c>
       <c r="D15" t="n">
-        <v>6.505570797145574</v>
+        <v>6.816745549483643</v>
       </c>
       <c r="E15" t="n">
-        <v>18.47632489681525</v>
+        <v>17.78394732839519</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.968364877106685</v>
+        <v>1.87613949776974</v>
       </c>
       <c r="C16" t="n">
-        <v>12.31384546987281</v>
+        <v>11.03604192793333</v>
       </c>
       <c r="D16" t="n">
-        <v>6.954946173810465</v>
+        <v>7.350138894677977</v>
       </c>
       <c r="E16" t="n">
-        <v>21.23715652078996</v>
+        <v>20.26232032038105</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.589017564185718</v>
+        <v>1.499472356081366</v>
       </c>
       <c r="C17" t="n">
-        <v>11.51186558775063</v>
+        <v>10.16714612228969</v>
       </c>
       <c r="D17" t="n">
-        <v>6.430624177403374</v>
+        <v>6.869269051660847</v>
       </c>
       <c r="E17" t="n">
-        <v>19.53150732933972</v>
+        <v>18.5358875300319</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.806563037969768</v>
+        <v>1.703479529023853</v>
       </c>
       <c r="C18" t="n">
-        <v>13.49436763179847</v>
+        <v>11.93067915838232</v>
       </c>
       <c r="D18" t="n">
-        <v>6.831795741789747</v>
+        <v>7.394101556874149</v>
       </c>
       <c r="E18" t="n">
-        <v>22.13272641155799</v>
+        <v>21.02826024428032</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.802665499583908</v>
+        <v>1.701133152010704</v>
       </c>
       <c r="C19" t="n">
-        <v>14.48040557351284</v>
+        <v>12.82185081943532</v>
       </c>
       <c r="D19" t="n">
-        <v>6.899192721686291</v>
+        <v>7.514768167203125</v>
       </c>
       <c r="E19" t="n">
-        <v>23.18226379478304</v>
+        <v>22.03775213864915</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1.987587497155838</v>
+        <v>1.880861704227167</v>
       </c>
       <c r="C20" t="n">
-        <v>16.62167585629147</v>
+        <v>14.80801478242</v>
       </c>
       <c r="D20" t="n">
-        <v>7.326282425464782</v>
+        <v>8.065243922451353</v>
       </c>
       <c r="E20" t="n">
-        <v>25.93554577891209</v>
+        <v>24.75412040909852</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>1.169408777913588</v>
+        <v>1.111083146804285</v>
       </c>
       <c r="C21" t="n">
-        <v>12.1547728893537</v>
+        <v>10.99950127838127</v>
       </c>
       <c r="D21" t="n">
-        <v>6.102219752855772</v>
+        <v>6.763495554005297</v>
       </c>
       <c r="E21" t="n">
-        <v>19.42640142012306</v>
+        <v>18.87407997919085</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_total_coral_cover_iteration_60_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_60_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.26157175266936</v>
+        <v>1.278801424878891</v>
       </c>
       <c r="C3" t="n">
-        <v>4.670759823541673</v>
+        <v>4.68291386012025</v>
       </c>
       <c r="D3" t="n">
-        <v>6.082089110114832</v>
+        <v>6.128584681387959</v>
       </c>
       <c r="E3" t="n">
-        <v>12.01442068632586</v>
+        <v>12.0902999663871</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.391877831645445</v>
+        <v>1.441089675807414</v>
       </c>
       <c r="C4" t="n">
-        <v>5.231826807628022</v>
+        <v>5.289701573022196</v>
       </c>
       <c r="D4" t="n">
-        <v>6.40837259049153</v>
+        <v>6.357349634569004</v>
       </c>
       <c r="E4" t="n">
-        <v>13.032077229765</v>
+        <v>13.08814088339861</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.570846606901767</v>
+        <v>1.665657969941635</v>
       </c>
       <c r="C5" t="n">
-        <v>5.964971877421607</v>
+        <v>6.107929353835799</v>
       </c>
       <c r="D5" t="n">
-        <v>6.768378191450608</v>
+        <v>6.673261112770466</v>
       </c>
       <c r="E5" t="n">
-        <v>14.30419667577398</v>
+        <v>14.4468484365479</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.771152915485142</v>
+        <v>1.919852190801662</v>
       </c>
       <c r="C6" t="n">
-        <v>6.861645218226421</v>
+        <v>7.089737257255121</v>
       </c>
       <c r="D6" t="n">
-        <v>7.216835116327973</v>
+        <v>6.954341265912807</v>
       </c>
       <c r="E6" t="n">
-        <v>15.84963325003953</v>
+        <v>15.96393071396959</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>2.002312797362219</v>
+        <v>2.213905641550973</v>
       </c>
       <c r="C7" t="n">
-        <v>7.880251905912391</v>
+        <v>8.266511765516496</v>
       </c>
       <c r="D7" t="n">
-        <v>7.677675803634386</v>
+        <v>7.31580579283884</v>
       </c>
       <c r="E7" t="n">
-        <v>17.560240506909</v>
+        <v>17.79622319990631</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.223186607476612</v>
+        <v>1.433310143587454</v>
       </c>
       <c r="C8" t="n">
-        <v>5.465112561929987</v>
+        <v>5.906596617089523</v>
       </c>
       <c r="D8" t="n">
-        <v>5.87102654243543</v>
+        <v>5.497332915963105</v>
       </c>
       <c r="E8" t="n">
-        <v>12.55932571184203</v>
+        <v>12.83723967664008</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.527262609843897</v>
+        <v>1.833768035119105</v>
       </c>
       <c r="C9" t="n">
-        <v>6.667114235774661</v>
+        <v>7.31192620011284</v>
       </c>
       <c r="D9" t="n">
-        <v>6.498929460487083</v>
+        <v>5.911326851071254</v>
       </c>
       <c r="E9" t="n">
-        <v>14.69330630610564</v>
+        <v>15.0570210863032</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.843953332620659</v>
+        <v>2.268442715053516</v>
       </c>
       <c r="C10" t="n">
-        <v>7.970523643037298</v>
+        <v>8.867112109127406</v>
       </c>
       <c r="D10" t="n">
-        <v>7.110485455354424</v>
+        <v>6.307214494128325</v>
       </c>
       <c r="E10" t="n">
-        <v>16.92496243101238</v>
+        <v>17.44276931830925</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.16548641037249</v>
+        <v>2.705268528042768</v>
       </c>
       <c r="C11" t="n">
-        <v>9.32984362864272</v>
+        <v>10.50688210425479</v>
       </c>
       <c r="D11" t="n">
-        <v>7.731927171112607</v>
+        <v>6.779276063740969</v>
       </c>
       <c r="E11" t="n">
-        <v>19.22725721012782</v>
+        <v>19.99142669603853</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.477023487420702</v>
+        <v>3.13397602916538</v>
       </c>
       <c r="C12" t="n">
-        <v>10.78196032205523</v>
+        <v>12.23447513388197</v>
       </c>
       <c r="D12" t="n">
-        <v>8.339132958918649</v>
+        <v>7.141469147936297</v>
       </c>
       <c r="E12" t="n">
-        <v>21.59811676839458</v>
+        <v>22.50992031098365</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.778315504960552</v>
+        <v>3.557171619307359</v>
       </c>
       <c r="C13" t="n">
-        <v>12.29476581349462</v>
+        <v>14.0256266472803</v>
       </c>
       <c r="D13" t="n">
-        <v>8.863241510599318</v>
+        <v>7.490498453983726</v>
       </c>
       <c r="E13" t="n">
-        <v>23.93632282905449</v>
+        <v>25.07329672057138</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.599679344253838</v>
+        <v>2.016499967045907</v>
       </c>
       <c r="C14" t="n">
-        <v>8.715936483349099</v>
+        <v>9.850993909091089</v>
       </c>
       <c r="D14" t="n">
-        <v>6.734612536546355</v>
+        <v>5.674089396510781</v>
       </c>
       <c r="E14" t="n">
-        <v>17.05022836414929</v>
+        <v>17.54158327264778</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.624861172867768</v>
+        <v>2.121723685987079</v>
       </c>
       <c r="C15" t="n">
-        <v>9.342340606043775</v>
+        <v>10.70293493188239</v>
       </c>
       <c r="D15" t="n">
-        <v>6.816745549483643</v>
+        <v>5.613299578663818</v>
       </c>
       <c r="E15" t="n">
-        <v>17.78394732839519</v>
+        <v>18.43795819653328</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.87613949776974</v>
+        <v>2.501434245558618</v>
       </c>
       <c r="C16" t="n">
-        <v>11.03604192793333</v>
+        <v>12.68512281666487</v>
       </c>
       <c r="D16" t="n">
-        <v>7.350138894677977</v>
+        <v>5.99672114455741</v>
       </c>
       <c r="E16" t="n">
-        <v>20.26232032038105</v>
+        <v>21.18327820678089</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.499472356081366</v>
+        <v>2.034495402464751</v>
       </c>
       <c r="C17" t="n">
-        <v>10.16714612228969</v>
+        <v>11.65754712958381</v>
       </c>
       <c r="D17" t="n">
-        <v>6.869269051660847</v>
+        <v>5.484101580784937</v>
       </c>
       <c r="E17" t="n">
-        <v>18.5358875300319</v>
+        <v>19.1761441128335</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.703479529023853</v>
+        <v>2.336029392347116</v>
       </c>
       <c r="C18" t="n">
-        <v>11.93067915838232</v>
+        <v>13.60743551489658</v>
       </c>
       <c r="D18" t="n">
-        <v>7.394101556874149</v>
+        <v>5.802138749575692</v>
       </c>
       <c r="E18" t="n">
-        <v>21.02826024428032</v>
+        <v>21.74560365681938</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.701133152010704</v>
+        <v>2.351325021579281</v>
       </c>
       <c r="C19" t="n">
-        <v>12.82185081943532</v>
+        <v>14.52214948589742</v>
       </c>
       <c r="D19" t="n">
-        <v>7.514768167203125</v>
+        <v>5.827831086995831</v>
       </c>
       <c r="E19" t="n">
-        <v>22.03775213864915</v>
+        <v>22.70130559447253</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1.880861704227167</v>
+        <v>2.606903401425853</v>
       </c>
       <c r="C20" t="n">
-        <v>14.80801478242</v>
+        <v>16.61110243351673</v>
       </c>
       <c r="D20" t="n">
-        <v>8.065243922451353</v>
+        <v>6.15606861443371</v>
       </c>
       <c r="E20" t="n">
-        <v>24.75412040909852</v>
+        <v>25.3740744493763</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>1.111083146804285</v>
+        <v>1.53890916136096</v>
       </c>
       <c r="C21" t="n">
-        <v>10.99950127838127</v>
+        <v>12.14171564488722</v>
       </c>
       <c r="D21" t="n">
-        <v>6.763495554005297</v>
+        <v>5.095084052977139</v>
       </c>
       <c r="E21" t="n">
-        <v>18.87407997919085</v>
+        <v>18.77570885922531</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_total_coral_cover_iteration_60_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_60_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.278801424878891</v>
+        <v>2.600364483599098</v>
       </c>
       <c r="C3" t="n">
-        <v>4.68291386012025</v>
+        <v>7.680150554817049</v>
       </c>
       <c r="D3" t="n">
-        <v>6.128584681387959</v>
+        <v>8.173116165251416</v>
       </c>
       <c r="E3" t="n">
-        <v>12.0902999663871</v>
+        <v>18.45363120366756</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.441089675807414</v>
+        <v>1.099582032393215</v>
       </c>
       <c r="C4" t="n">
-        <v>5.289701573022196</v>
+        <v>4.464798080324097</v>
       </c>
       <c r="D4" t="n">
-        <v>6.357349634569004</v>
+        <v>5.835763939691658</v>
       </c>
       <c r="E4" t="n">
-        <v>13.08814088339861</v>
+        <v>11.40014405240897</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.665657969941635</v>
+        <v>1.219381162901861</v>
       </c>
       <c r="C5" t="n">
-        <v>6.107929353835799</v>
+        <v>5.112990190356631</v>
       </c>
       <c r="D5" t="n">
-        <v>6.673261112770466</v>
+        <v>6.219481599010737</v>
       </c>
       <c r="E5" t="n">
-        <v>14.4468484365479</v>
+        <v>12.55185295226923</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.919852190801662</v>
+        <v>1.359955437478415</v>
       </c>
       <c r="C6" t="n">
-        <v>7.089737257255121</v>
+        <v>5.935492745539108</v>
       </c>
       <c r="D6" t="n">
-        <v>6.954341265912807</v>
+        <v>6.588084930049272</v>
       </c>
       <c r="E6" t="n">
-        <v>15.96393071396959</v>
+        <v>13.88353311306679</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>2.213905641550973</v>
+        <v>1.511061431870667</v>
       </c>
       <c r="C7" t="n">
-        <v>8.266511765516496</v>
+        <v>6.897778192717874</v>
       </c>
       <c r="D7" t="n">
-        <v>7.31580579283884</v>
+        <v>7.081556912163611</v>
       </c>
       <c r="E7" t="n">
-        <v>17.79622319990631</v>
+        <v>15.49039653675215</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.433310143587454</v>
+        <v>1.676050059658214</v>
       </c>
       <c r="C8" t="n">
-        <v>5.906596617089523</v>
+        <v>7.961410137109286</v>
       </c>
       <c r="D8" t="n">
-        <v>5.497332915963105</v>
+        <v>7.626496105057686</v>
       </c>
       <c r="E8" t="n">
-        <v>12.83723967664008</v>
+        <v>17.26395630182519</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.833768035119105</v>
+        <v>1.823676768630201</v>
       </c>
       <c r="C9" t="n">
-        <v>7.31192620011284</v>
+        <v>9.11497579558203</v>
       </c>
       <c r="D9" t="n">
-        <v>5.911326851071254</v>
+        <v>8.124207268273336</v>
       </c>
       <c r="E9" t="n">
-        <v>15.0570210863032</v>
+        <v>19.06285983248557</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.268442715053516</v>
+        <v>1.123580795079347</v>
       </c>
       <c r="C10" t="n">
-        <v>8.867112109127406</v>
+        <v>6.67922233107275</v>
       </c>
       <c r="D10" t="n">
-        <v>6.307214494128325</v>
+        <v>6.435199121705162</v>
       </c>
       <c r="E10" t="n">
-        <v>17.44276931830925</v>
+        <v>14.23800224785726</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.705268528042768</v>
+        <v>1.06949631405239</v>
       </c>
       <c r="C11" t="n">
-        <v>10.50688210425479</v>
+        <v>7.007175151676397</v>
       </c>
       <c r="D11" t="n">
-        <v>6.779276063740969</v>
+        <v>6.385021996541109</v>
       </c>
       <c r="E11" t="n">
-        <v>19.99142669603853</v>
+        <v>14.4616934622699</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.13397602916538</v>
+        <v>1.165805763839002</v>
       </c>
       <c r="C12" t="n">
-        <v>12.23447513388197</v>
+        <v>8.218877620688938</v>
       </c>
       <c r="D12" t="n">
-        <v>7.141469147936297</v>
+        <v>6.86598019685162</v>
       </c>
       <c r="E12" t="n">
-        <v>22.50992031098365</v>
+        <v>16.25066358137956</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.557171619307359</v>
+        <v>0.9256211879950202</v>
       </c>
       <c r="C13" t="n">
-        <v>14.0256266472803</v>
+        <v>7.785259294677205</v>
       </c>
       <c r="D13" t="n">
-        <v>7.490498453983726</v>
+        <v>6.358946777516313</v>
       </c>
       <c r="E13" t="n">
-        <v>25.07329672057138</v>
+        <v>15.06982726018854</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2.016499967045907</v>
+        <v>1.014636252339079</v>
       </c>
       <c r="C14" t="n">
-        <v>9.850993909091089</v>
+        <v>9.071937835863077</v>
       </c>
       <c r="D14" t="n">
-        <v>5.674089396510781</v>
+        <v>6.782197847771198</v>
       </c>
       <c r="E14" t="n">
-        <v>17.54158327264778</v>
+        <v>16.86877193597335</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>2.121723685987079</v>
+        <v>0.9955216245373933</v>
       </c>
       <c r="C15" t="n">
-        <v>10.70293493188239</v>
+        <v>9.765738938454298</v>
       </c>
       <c r="D15" t="n">
-        <v>5.613299578663818</v>
+        <v>6.913359341058571</v>
       </c>
       <c r="E15" t="n">
-        <v>18.43795819653328</v>
+        <v>17.67461990405026</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>2.501434245558618</v>
+        <v>1.095993684590012</v>
       </c>
       <c r="C16" t="n">
-        <v>12.68512281666487</v>
+        <v>11.40215528180105</v>
       </c>
       <c r="D16" t="n">
-        <v>5.99672114455741</v>
+        <v>7.415169862607286</v>
       </c>
       <c r="E16" t="n">
-        <v>21.18327820678089</v>
+        <v>19.91331882899835</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2.034495402464751</v>
+        <v>0.6589785115215866</v>
       </c>
       <c r="C17" t="n">
-        <v>11.65754712958381</v>
+        <v>8.583773607403392</v>
       </c>
       <c r="D17" t="n">
-        <v>5.484101580784937</v>
+        <v>6.212882354078473</v>
       </c>
       <c r="E17" t="n">
-        <v>19.1761441128335</v>
+        <v>15.45563447300345</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2.336029392347116</v>
+        <v>0.5261284121829082</v>
       </c>
       <c r="C18" t="n">
-        <v>13.60743551489658</v>
+        <v>7.6141897572122</v>
       </c>
       <c r="D18" t="n">
-        <v>5.802138749575692</v>
+        <v>5.725307174241336</v>
       </c>
       <c r="E18" t="n">
-        <v>21.74560365681938</v>
+        <v>13.86562534363645</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2.351325021579281</v>
+        <v>0.6183439740428112</v>
       </c>
       <c r="C19" t="n">
-        <v>14.52214948589742</v>
+        <v>9.422785012929758</v>
       </c>
       <c r="D19" t="n">
-        <v>5.827831086995831</v>
+        <v>6.35197636881616</v>
       </c>
       <c r="E19" t="n">
-        <v>22.70130559447253</v>
+        <v>16.39310535578873</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>2.606903401425853</v>
+        <v>0.7056606148585224</v>
       </c>
       <c r="C20" t="n">
-        <v>16.61110243351673</v>
+        <v>11.34908200090947</v>
       </c>
       <c r="D20" t="n">
-        <v>6.15606861443371</v>
+        <v>6.95861791022435</v>
       </c>
       <c r="E20" t="n">
-        <v>25.3740744493763</v>
+        <v>19.01336052599234</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>1.53890916136096</v>
+        <v>0.7871849442191776</v>
       </c>
       <c r="C21" t="n">
-        <v>12.14171564488722</v>
+        <v>13.28764101771522</v>
       </c>
       <c r="D21" t="n">
-        <v>5.095084052977139</v>
+        <v>7.540411417238052</v>
       </c>
       <c r="E21" t="n">
-        <v>18.77570885922531</v>
+        <v>21.61523737917245</v>
       </c>
     </row>
   </sheetData>
